--- a/docs/ValueSet-BRCaraterAtendimentoMIRA.xlsx
+++ b/docs/ValueSet-BRCaraterAtendimentoMIRA.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.0-release</t>
   </si>
   <si>
     <t>Name</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Ministério da Saúde do Brasil (http://www.saude.gov.br)</t>
+    <t>Ministério da Saúde do Brasil (http://www.saude.gov.br, cgiis.datasus@saude.gov.br)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
